--- a/Spark/Data/Simulated/Bruno/model_run/results/tukey_sp_vs_system&costs.xlsx
+++ b/Spark/Data/Simulated/Bruno/model_run/results/tukey_sp_vs_system&costs.xlsx
@@ -424,10 +424,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.05312372383171</v>
+        <v>1.23173382612437</v>
       </c>
       <c r="D2">
-        <v>0.233835574378124</v>
+        <v>0.289439624948271</v>
       </c>
       <c r="E2" t="e">
         <v>#NUM!</v>
@@ -436,10 +436,10 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0.233114423468406</v>
+        <v>0.886960113106863</v>
       </c>
       <c r="H2">
-        <v>0.999347665748523</v>
+        <v>0.901834218651268</v>
       </c>
     </row>
     <row r="3">
@@ -452,10 +452,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>1.99268707932983</v>
+        <v>2.81376139633862</v>
       </c>
       <c r="D3">
-        <v>0.443890626627761</v>
+        <v>0.660934499380199</v>
       </c>
       <c r="E3" t="e">
         <v>#NUM!</v>
@@ -464,10 +464,10 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>3.0951901520664</v>
+        <v>4.40421634811898</v>
       </c>
       <c r="H3">
-        <v>0.0168353919031546</v>
+        <v>0.000103687957159981</v>
       </c>
     </row>
     <row r="4">
@@ -480,10 +480,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.225529844879104</v>
+        <v>0.272999772768399</v>
       </c>
       <c r="D4">
-        <v>0.0496521562478004</v>
+        <v>0.0636218743810176</v>
       </c>
       <c r="E4" t="e">
         <v>#NUM!</v>
@@ -492,10 +492,10 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>-6.76470570683136</v>
+        <v>-5.57090350992316</v>
       </c>
       <c r="H4">
-        <v>0.000000000133589694861769</v>
+        <v>0.000000252699951519553</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.513157284208645</v>
+        <v>0.653147345341144</v>
       </c>
       <c r="D5">
-        <v>0.0980663488501484</v>
+        <v>0.132382143348836</v>
       </c>
       <c r="E5" t="e">
         <v>#NUM!</v>
@@ -520,10 +520,10 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>-3.49115297160001</v>
+        <v>-2.10156565017922</v>
       </c>
       <c r="H5">
-        <v>0.00438447514482143</v>
+        <v>0.219274939162576</v>
       </c>
     </row>
     <row r="6">
@@ -536,10 +536,10 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1.89216806557124</v>
+        <v>2.28439078042703</v>
       </c>
       <c r="D6">
-        <v>0.336253208321877</v>
+        <v>0.423694903737479</v>
       </c>
       <c r="E6" t="e">
         <v>#NUM!</v>
@@ -548,10 +548,10 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>3.58860414117873</v>
+        <v>4.45399218229008</v>
       </c>
       <c r="H6">
-        <v>0.00306623645635151</v>
+        <v>0.0000824724279145927</v>
       </c>
     </row>
     <row r="7">
@@ -564,10 +564,10 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.214153227940332</v>
+        <v>0.221638609720891</v>
       </c>
       <c r="D7">
-        <v>0.0373558360540884</v>
+        <v>0.0405906368646354</v>
       </c>
       <c r="E7" t="e">
         <v>#NUM!</v>
@@ -576,10 +576,10 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>-8.83459609594759</v>
+        <v>-8.22713055031253</v>
       </c>
       <c r="H7">
-        <v>0.0000000000000373034936274053</v>
+        <v>0.0000000000000589528426075958</v>
       </c>
     </row>
     <row r="8">
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.487271602183227</v>
+        <v>0.530266630247755</v>
       </c>
       <c r="D8">
-        <v>0.0662382067629062</v>
+        <v>0.0755604128068246</v>
       </c>
       <c r="E8" t="e">
         <v>#NUM!</v>
@@ -604,10 +604,10 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>-5.28872908108311</v>
+        <v>-4.45190877527357</v>
       </c>
       <c r="H8">
-        <v>0.00000122561267679178</v>
+        <v>0.000083270646274558</v>
       </c>
     </row>
     <row r="9">
@@ -620,10 +620,10 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.113178756071903</v>
+        <v>0.0970230713676141</v>
       </c>
       <c r="D9">
-        <v>0.0198459566500593</v>
+        <v>0.017756459567211</v>
       </c>
       <c r="E9" t="e">
         <v>#NUM!</v>
@@ -632,7 +632,7 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>-12.4253208799913</v>
+        <v>-12.7466879701603</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -648,10 +648,10 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.257520254701119</v>
+        <v>0.232126059512738</v>
       </c>
       <c r="D10">
-        <v>0.0353084934784946</v>
+        <v>0.0330383576692931</v>
       </c>
       <c r="E10" t="e">
         <v>#NUM!</v>
@@ -660,10 +660,10 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>-9.89469095869243</v>
+        <v>-10.2612314855916</v>
       </c>
       <c r="H10">
-        <v>0.0000000000000454081217071689</v>
+        <v>0.0000000000000393018950717305</v>
       </c>
     </row>
     <row r="11">
@@ -676,10 +676,10 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>2.27534091766757</v>
+        <v>2.39248310984949</v>
       </c>
       <c r="D11">
-        <v>0.302254002268889</v>
+        <v>0.333220687684172</v>
       </c>
       <c r="E11" t="e">
         <v>#NUM!</v>
@@ -688,10 +688,10 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>6.18891983532765</v>
+        <v>6.26323376130891</v>
       </c>
       <c r="H11">
-        <v>0.00000000605308625445389</v>
+        <v>0.00000000376827713477468</v>
       </c>
     </row>
     <row r="12">
@@ -704,10 +704,10 @@
         <v>0.1</v>
       </c>
       <c r="C12">
-        <v>1.08268086751302</v>
+        <v>1.23868814364213</v>
       </c>
       <c r="D12">
-        <v>0.239622742902084</v>
+        <v>0.288333590358298</v>
       </c>
       <c r="E12" t="e">
         <v>#NUM!</v>
@@ -716,10 +716,10 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>0.358932703306331</v>
+        <v>0.919576359417064</v>
       </c>
       <c r="H12">
-        <v>0.996457987319868</v>
+        <v>0.889473200849929</v>
       </c>
     </row>
     <row r="13">
@@ -732,10 +732,10 @@
         <v>0.1</v>
       </c>
       <c r="C13">
-        <v>1.38111457126649</v>
+        <v>1.86393545632598</v>
       </c>
       <c r="D13">
-        <v>0.306887285727917</v>
+        <v>0.434564094507496</v>
       </c>
       <c r="E13" t="e">
         <v>#NUM!</v>
@@ -744,10 +744,10 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1.45313688721923</v>
+        <v>2.67084683315296</v>
       </c>
       <c r="H13">
-        <v>0.593101307630399</v>
+        <v>0.0583479505762521</v>
       </c>
     </row>
     <row r="14">
@@ -760,10 +760,10 @@
         <v>0.1</v>
       </c>
       <c r="C14">
-        <v>0.228504436736928</v>
+        <v>0.266523820797448</v>
       </c>
       <c r="D14">
-        <v>0.0501492130660687</v>
+        <v>0.0615452548545759</v>
       </c>
       <c r="E14" t="e">
         <v>#NUM!</v>
@@ -772,10 +772,10 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>-6.72629039178136</v>
+        <v>-5.72622901748118</v>
       </c>
       <c r="H14">
-        <v>0.000000000174040004630172</v>
+        <v>0.000000102473901253397</v>
       </c>
     </row>
     <row r="15">
@@ -788,10 +788,10 @@
         <v>0.1</v>
       </c>
       <c r="C15">
-        <v>0.512571843340856</v>
+        <v>0.62838708187235</v>
       </c>
       <c r="D15">
-        <v>0.0976170691561235</v>
+        <v>0.126071624791819</v>
       </c>
       <c r="E15" t="e">
         <v>#NUM!</v>
@@ -800,10 +800,10 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>-3.50921354921763</v>
+        <v>-2.31573096909397</v>
       </c>
       <c r="H15">
-        <v>0.00410649962976828</v>
+        <v>0.139786095710633</v>
       </c>
     </row>
     <row r="16">
@@ -816,10 +816,10 @@
         <v>0.1</v>
       </c>
       <c r="C16">
-        <v>1.27564327837341</v>
+        <v>1.50476572000231</v>
       </c>
       <c r="D16">
-        <v>0.226437402483842</v>
+        <v>0.278201998815887</v>
       </c>
       <c r="E16" t="e">
         <v>#NUM!</v>
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>1.37148764721598</v>
+        <v>2.21027627640497</v>
       </c>
       <c r="H16">
-        <v>0.646028094487119</v>
+        <v>0.175766408514274</v>
       </c>
     </row>
     <row r="17">
@@ -844,10 +844,10 @@
         <v>0.1</v>
       </c>
       <c r="C17">
-        <v>0.211054285333235</v>
+        <v>0.215166199955532</v>
       </c>
       <c r="D17">
-        <v>0.0367386178396203</v>
+        <v>0.0391761906115203</v>
       </c>
       <c r="E17" t="e">
         <v>#NUM!</v>
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>-8.93676700670326</v>
+        <v>-8.43801830691671</v>
       </c>
       <c r="H17">
-        <v>0.0000000000000345279360658424</v>
+        <v>0.0000000000000491828799908944</v>
       </c>
     </row>
     <row r="18">
@@ -872,10 +872,10 @@
         <v>0.1</v>
       </c>
       <c r="C18">
-        <v>0.473428374621842</v>
+        <v>0.507300473567702</v>
       </c>
       <c r="D18">
-        <v>0.0642272625526845</v>
+        <v>0.0718778719640093</v>
       </c>
       <c r="E18" t="e">
         <v>#NUM!</v>
@@ -884,10 +884,10 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>-5.51180686341608</v>
+        <v>-4.78979650591794</v>
       </c>
       <c r="H18">
-        <v>0.000000354031168603441</v>
+        <v>0.0000164906769055673</v>
       </c>
     </row>
     <row r="19">
@@ -900,10 +900,10 @@
         <v>0.1</v>
       </c>
       <c r="C19">
-        <v>0.165449298335466</v>
+        <v>0.142989833630182</v>
       </c>
       <c r="D19">
-        <v>0.0289847885261631</v>
+        <v>0.026101430788044</v>
       </c>
       <c r="E19" t="e">
         <v>#NUM!</v>
@@ -912,10 +912,10 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>-10.2694645576187</v>
+        <v>-10.6550716837401</v>
       </c>
       <c r="H19">
-        <v>0.0000000000000555111512312578</v>
+        <v>0.000000000000046074255521944</v>
       </c>
     </row>
     <row r="20">
@@ -928,10 +928,10 @@
         <v>0.1</v>
       </c>
       <c r="C20">
-        <v>0.371129125711002</v>
+        <v>0.337129206775738</v>
       </c>
       <c r="D20">
-        <v>0.0508794497325798</v>
+        <v>0.0479678180243624</v>
       </c>
       <c r="E20" t="e">
         <v>#NUM!</v>
@@ -940,10 +940,10 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>-7.23013185172417</v>
+        <v>-7.64172521663567</v>
       </c>
       <c r="H20">
-        <v>0.00000000000486000129029662</v>
+        <v>0.000000000000245470310744622</v>
       </c>
     </row>
     <row r="21">
@@ -956,10 +956,10 @@
         <v>0.1</v>
       </c>
       <c r="C21">
-        <v>2.24315926053974</v>
+        <v>2.35771451869553</v>
       </c>
       <c r="D21">
-        <v>0.297471317675313</v>
+        <v>0.326829741374871</v>
       </c>
       <c r="E21" t="e">
         <v>#NUM!</v>
@@ -968,10 +968,10 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>6.09206732421131</v>
+        <v>6.18730285394274</v>
       </c>
       <c r="H21">
-        <v>0.0000000111354607756908</v>
+        <v>0.00000000611546413509245</v>
       </c>
     </row>
     <row r="22">
@@ -984,10 +984,10 @@
         <v>0.3</v>
       </c>
       <c r="C22">
-        <v>1.13401716461754</v>
+        <v>1.24428347785114</v>
       </c>
       <c r="D22">
-        <v>0.250148027191558</v>
+        <v>0.286685818579662</v>
       </c>
       <c r="E22" t="e">
         <v>#NUM!</v>
@@ -996,10 +996,10 @@
         <v>1</v>
       </c>
       <c r="G22">
-        <v>0.570147171003167</v>
+        <v>0.948600822704976</v>
       </c>
       <c r="H22">
-        <v>0.979391955128918</v>
+        <v>0.877773889181212</v>
       </c>
     </row>
     <row r="23">
@@ -1012,10 +1012,10 @@
         <v>0.3</v>
       </c>
       <c r="C23">
-        <v>0.764417064011289</v>
+        <v>0.927459988102119</v>
       </c>
       <c r="D23">
-        <v>0.169410567395362</v>
+        <v>0.214467145777986</v>
       </c>
       <c r="E23" t="e">
         <v>#NUM!</v>
@@ -1024,10 +1024,10 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>-1.21216955921619</v>
+        <v>-0.325658057139134</v>
       </c>
       <c r="H23">
-        <v>0.744335098515254</v>
+        <v>0.997574382719176</v>
       </c>
     </row>
     <row r="24">
@@ -1040,10 +1040,10 @@
         <v>0.3</v>
       </c>
       <c r="C24">
-        <v>0.241256340043382</v>
+        <v>0.259037210919364</v>
       </c>
       <c r="D24">
-        <v>0.0527743156470095</v>
+        <v>0.0592207857168504</v>
       </c>
       <c r="E24" t="e">
         <v>#NUM!</v>
@@ -1052,10 +1052,10 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>-6.50015527323232</v>
+        <v>-5.90845259299003</v>
       </c>
       <c r="H24">
-        <v>0.000000000802093280682925</v>
+        <v>0.0000000344843938959727</v>
       </c>
     </row>
     <row r="25">
@@ -1068,10 +1068,10 @@
         <v>0.3</v>
       </c>
       <c r="C25">
-        <v>0.530594730827056</v>
+        <v>0.598445040496986</v>
       </c>
       <c r="D25">
-        <v>0.100685863230571</v>
+        <v>0.118728358530205</v>
       </c>
       <c r="E25" t="e">
         <v>#NUM!</v>
@@ -1080,10 +1080,10 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>-3.33977373680563</v>
+        <v>-2.58787376284349</v>
       </c>
       <c r="H25">
-        <v>0.0074858860796061</v>
+        <v>0.072563212117256</v>
       </c>
     </row>
     <row r="26">
@@ -1096,10 +1096,10 @@
         <v>0.3</v>
       </c>
       <c r="C26">
-        <v>0.674078918610636</v>
+        <v>0.745376760691084</v>
       </c>
       <c r="D26">
-        <v>0.119519075153509</v>
+        <v>0.137347437540122</v>
       </c>
       <c r="E26" t="e">
         <v>#NUM!</v>
@@ -1108,10 +1108,10 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>-2.2244330043968</v>
+        <v>-1.59479125037629</v>
       </c>
       <c r="H26">
-        <v>0.170584960400366</v>
+        <v>0.500688557708706</v>
       </c>
     </row>
     <row r="27">
@@ -1124,10 +1124,10 @@
         <v>0.3</v>
       </c>
       <c r="C27">
-        <v>0.212744875096092</v>
+        <v>0.20818182956726</v>
       </c>
       <c r="D27">
-        <v>0.0369544429621263</v>
+        <v>0.0376742756477387</v>
       </c>
       <c r="E27" t="e">
         <v>#NUM!</v>
@@ -1136,10 +1136,10 @@
         <v>1</v>
       </c>
       <c r="G27">
-        <v>-8.90981022941729</v>
+        <v>-8.67193263114051</v>
       </c>
       <c r="H27">
-        <v>0.0000000000000359712259978551</v>
+        <v>0.0000000000000421884749357559</v>
       </c>
     </row>
     <row r="28">
@@ -1152,10 +1152,10 @@
         <v>0.3</v>
       </c>
       <c r="C28">
-        <v>0.467889505892979</v>
+        <v>0.480955546826428</v>
       </c>
       <c r="D28">
-        <v>0.0633488055331282</v>
+        <v>0.0677462432905731</v>
       </c>
       <c r="E28" t="e">
         <v>#NUM!</v>
@@ -1164,10 +1164,10 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>-5.6097804750781</v>
+        <v>-5.19659883034721</v>
       </c>
       <c r="H28">
-        <v>0.000000202049681097272</v>
+        <v>0.00000201775718711161</v>
       </c>
     </row>
     <row r="29">
@@ -1180,10 +1180,10 @@
         <v>0.3</v>
       </c>
       <c r="C29">
-        <v>0.315608260727968</v>
+        <v>0.279297451364384</v>
       </c>
       <c r="D29">
-        <v>0.0552363163492689</v>
+        <v>0.0508409301871224</v>
       </c>
       <c r="E29" t="e">
         <v>#NUM!</v>
@@ -1192,10 +1192,10 @@
         <v>1</v>
       </c>
       <c r="G29">
-        <v>-6.58943898357584</v>
+        <v>-7.00690829479461</v>
       </c>
       <c r="H29">
-        <v>0.000000000441387482119637</v>
+        <v>0.0000000000243977060776501</v>
       </c>
     </row>
     <row r="30">
@@ -1208,10 +1208,10 @@
         <v>0.3</v>
       </c>
       <c r="C30">
-        <v>0.694116805873947</v>
+        <v>0.645251599178522</v>
       </c>
       <c r="D30">
-        <v>0.0951441232542056</v>
+        <v>0.0917684935059144</v>
       </c>
       <c r="E30" t="e">
         <v>#NUM!</v>
@@ -1220,10 +1220,10 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>-2.66366924080983</v>
+        <v>-3.08051673352004</v>
       </c>
       <c r="H30">
-        <v>0.0594784899123945</v>
+        <v>0.01763625048574</v>
       </c>
     </row>
     <row r="31">
@@ -1236,10 +1236,10 @@
         <v>0.3</v>
       </c>
       <c r="C31">
-        <v>2.19929859970372</v>
+        <v>2.31026669246866</v>
       </c>
       <c r="D31">
-        <v>0.291133843230226</v>
+        <v>0.318642101137814</v>
       </c>
       <c r="E31" t="e">
         <v>#NUM!</v>
@@ -1248,10 +1248,10 @@
         <v>1</v>
       </c>
       <c r="G31">
-        <v>5.95379726681159</v>
+        <v>6.07117443124197</v>
       </c>
       <c r="H31">
-        <v>0.0000000261652060018491</v>
+        <v>0.000000012685039019189</v>
       </c>
     </row>
     <row r="32">
@@ -1264,10 +1264,10 @@
         <v>0.5</v>
       </c>
       <c r="C32">
-        <v>1.09469631148058</v>
+        <v>1.14685541794726</v>
       </c>
       <c r="D32">
-        <v>0.241360876353065</v>
+        <v>0.262920555042889</v>
       </c>
       <c r="E32" t="e">
         <v>#NUM!</v>
@@ -1276,10 +1276,10 @@
         <v>1</v>
       </c>
       <c r="G32">
-        <v>0.410359880252512</v>
+        <v>0.597695611833059</v>
       </c>
       <c r="H32">
-        <v>0.994058080068953</v>
+        <v>0.975472575496176</v>
       </c>
     </row>
     <row r="33">
@@ -1292,10 +1292,10 @@
         <v>0.5</v>
       </c>
       <c r="C33">
-        <v>0.465917853218519</v>
+        <v>0.492175746471442</v>
       </c>
       <c r="D33">
-        <v>0.103221129977626</v>
+        <v>0.113342349965963</v>
       </c>
       <c r="E33" t="e">
         <v>#NUM!</v>
@@ -1304,10 +1304,10 @@
         <v>1</v>
       </c>
       <c r="G33">
-        <v>-3.44738397392188</v>
+        <v>-3.07839870839239</v>
       </c>
       <c r="H33">
-        <v>0.00513113723897052</v>
+        <v>0.0177545939732207</v>
       </c>
     </row>
     <row r="34">
@@ -1320,10 +1320,10 @@
         <v>0.5</v>
       </c>
       <c r="C34">
-        <v>0.219186266284872</v>
+        <v>0.211369209503704</v>
       </c>
       <c r="D34">
-        <v>0.0479222609532076</v>
+        <v>0.0480893950802843</v>
       </c>
       <c r="E34" t="e">
         <v>#NUM!</v>
@@ -1332,10 +1332,10 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>-6.94224823114399</v>
+        <v>-6.8310116363061</v>
       </c>
       <c r="H34">
-        <v>0.0000000000386221055137526</v>
+        <v>0.0000000000843390912663722</v>
       </c>
     </row>
     <row r="35">
@@ -1348,10 +1348,10 @@
         <v>0.5</v>
       </c>
       <c r="C35">
-        <v>0.483391779613835</v>
+        <v>0.48953275773178</v>
       </c>
       <c r="D35">
-        <v>0.0916787495029007</v>
+        <v>0.0965786196013898</v>
       </c>
       <c r="E35" t="e">
         <v>#NUM!</v>
@@ -1360,10 +1360,10 @@
         <v>1</v>
       </c>
       <c r="G35">
-        <v>-3.83285038934923</v>
+        <v>-3.62062699498249</v>
       </c>
       <c r="H35">
-        <v>0.00119637621020452</v>
+        <v>0.00272016697968336</v>
       </c>
     </row>
     <row r="36">
@@ -1376,10 +1376,10 @@
         <v>0.5</v>
       </c>
       <c r="C36">
-        <v>0.42561379656826</v>
+        <v>0.429152392506789</v>
       </c>
       <c r="D36">
-        <v>0.0754610172430318</v>
+        <v>0.0789566433129228</v>
       </c>
       <c r="E36" t="e">
         <v>#NUM!</v>
@@ -1388,10 +1388,10 @@
         <v>1</v>
       </c>
       <c r="G36">
-        <v>-4.81797191972176</v>
+        <v>-4.59794807869962</v>
       </c>
       <c r="H36">
-        <v>0.000014333451007098</v>
+        <v>0.0000419425416602337</v>
       </c>
     </row>
     <row r="37">
@@ -1404,10 +1404,10 @@
         <v>0.5</v>
       </c>
       <c r="C37">
-        <v>0.200225636997371</v>
+        <v>0.184303275021388</v>
       </c>
       <c r="D37">
-        <v>0.0347699088205277</v>
+        <v>0.0332665728990582</v>
       </c>
       <c r="E37" t="e">
         <v>#NUM!</v>
@@ -1416,10 +1416,10 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>-9.26159940934467</v>
+        <v>-9.36942491601766</v>
       </c>
       <c r="H37">
-        <v>0.0000000000000536237720893951</v>
+        <v>0.0000000000000479616346638068</v>
       </c>
     </row>
     <row r="38">
@@ -1432,10 +1432,10 @@
         <v>0.5</v>
       </c>
       <c r="C38">
-        <v>0.44157614723306</v>
+        <v>0.426847839815751</v>
       </c>
       <c r="D38">
-        <v>0.0597733619123198</v>
+        <v>0.0599696835347122</v>
       </c>
       <c r="E38" t="e">
         <v>#NUM!</v>
@@ -1444,10 +1444,10 @@
         <v>1</v>
       </c>
       <c r="G38">
-        <v>-6.03858392300802</v>
+        <v>-6.05951804617971</v>
       </c>
       <c r="H38">
-        <v>0.0000000155304660243161</v>
+        <v>0.000000013638908891167</v>
       </c>
     </row>
     <row r="39">
@@ -1460,10 +1460,10 @@
         <v>0.5</v>
       </c>
       <c r="C39">
-        <v>0.470439724021632</v>
+        <v>0.429458808198239</v>
       </c>
       <c r="D39">
-        <v>0.0823267371195922</v>
+        <v>0.0780793996758812</v>
       </c>
       <c r="E39" t="e">
         <v>#NUM!</v>
@@ -1472,10 +1472,10 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <v>-4.3090823095035</v>
+        <v>-4.64900131329382</v>
       </c>
       <c r="H39">
-        <v>0.000159478357680598</v>
+        <v>0.0000328347518555594</v>
       </c>
     </row>
     <row r="40">
@@ -1488,10 +1488,10 @@
         <v>0.5</v>
       </c>
       <c r="C40">
-        <v>1.03750430741086</v>
+        <v>0.994629989879407</v>
       </c>
       <c r="D40">
-        <v>0.142227300560457</v>
+        <v>0.141413289306598</v>
       </c>
       <c r="E40" t="e">
         <v>#NUM!</v>
@@ -1500,10 +1500,10 @@
         <v>1</v>
       </c>
       <c r="G40">
-        <v>0.268576869257892</v>
+        <v>-0.0378717287732447</v>
       </c>
       <c r="H40">
-        <v>0.998860067868689</v>
+        <v>0.999999534247593</v>
       </c>
     </row>
     <row r="41">
@@ -1516,10 +1516,10 @@
         <v>0.5</v>
       </c>
       <c r="C41">
-        <v>2.20539264529275</v>
+        <v>2.31600789387066</v>
       </c>
       <c r="D41">
-        <v>0.291852274196069</v>
+        <v>0.3187723057293</v>
       </c>
       <c r="E41" t="e">
         <v>#NUM!</v>
@@ -1528,10 +1528,10 @@
         <v>1</v>
       </c>
       <c r="G41">
-        <v>5.9765075246055</v>
+        <v>6.10180853485626</v>
       </c>
       <c r="H41">
-        <v>0.0000000227690751808396</v>
+        <v>0.0000000104776243237126</v>
       </c>
     </row>
   </sheetData>
